--- a/examples/04_Si3N4_on_Si_70deg.xlsx
+++ b/examples/04_Si3N4_on_Si_70deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4049,10 +4049,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>Возможные дефекты</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/04_Si3N4_on_Si_70deg.xlsx
+++ b/examples/04_Si3N4_on_Si_70deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3971,100 +3971,112 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Угол падения, град</t>
+          <t>Задняя сторона подложки</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>70</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>нет (зачернена / матирована / отсечена)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Толщина (номинал), нм</t>
+          <t>Угол падения, град</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Толщина (номинал), нм</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Неопределённость толщины, %</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>±6</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Диапазон длин волн, нм</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>400 – 800, шаг 2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Спектральная полоса прибора, нм (FWHM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Шумовая модель</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>столбцы σΨ, σΔ — повторяемость прибора (σΔ растёт при Ψ → 0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RCE-эллипсометр с ПЗС, все длины волн одновременно; Δ в диапазоне 0–360°; конвенция N = n − ik (Аззам–Башара)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Возможные дефекты</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/04_Si3N4_on_Si_70deg.xlsx
+++ b/examples/04_Si3N4_on_Si_70deg.xlsx
@@ -478,16 +478,16 @@
         <v>400</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>60.359</v>
+        <v>61.0079</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>335.4363</v>
+        <v>336.9355</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.035</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.0896</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         <v>402</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>62.0807</v>
+        <v>62.0768</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8.042199999999999</v>
+        <v>10.6687</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0347</v>
@@ -512,16 +512,16 @@
         <v>404</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>56.2381</v>
+        <v>55.7456</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>34.412</v>
+        <v>36.2936</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.0344</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.0819</v>
+        <v>0.0813</v>
       </c>
     </row>
     <row r="5">
@@ -529,16 +529,16 @@
         <v>406</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>48.8306</v>
+        <v>48.3273</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>48.4452</v>
+        <v>49.6423</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0341</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.0756</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -546,16 +546,16 @@
         <v>408</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>42.6622</v>
+        <v>42.2892</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>56.6494</v>
+        <v>57.5684</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0337</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.0745</v>
+        <v>0.0746</v>
       </c>
     </row>
     <row r="7">
@@ -563,16 +563,16 @@
         <v>410</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>38.153</v>
+        <v>37.9001</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>62.4706</v>
+        <v>63.3144</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0334</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.0757</v>
+        <v>0.0759</v>
       </c>
     </row>
     <row r="8">
@@ -580,16 +580,16 @@
         <v>412</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>34.658</v>
+        <v>34.5001</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>67.9164</v>
+        <v>68.78319999999999</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0331</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.0779</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="9">
@@ -597,16 +597,16 @@
         <v>414</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>31.808</v>
+        <v>31.7347</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>73.2021</v>
+        <v>74.146</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0328</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.0805</v>
+        <v>0.0806</v>
       </c>
     </row>
     <row r="10">
@@ -614,10 +614,10 @@
         <v>416</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>29.589</v>
+        <v>29.5984</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>78.9186</v>
+        <v>79.9744</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0325</v>
@@ -631,16 +631,16 @@
         <v>418</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>27.4598</v>
+        <v>27.5557</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>85.3295</v>
+        <v>86.5239</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0322</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0863</v>
       </c>
     </row>
     <row r="12">
@@ -648,16 +648,16 @@
         <v>420</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>25.6554</v>
+        <v>25.8362</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>92.2273</v>
+        <v>93.5722</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0319</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.09</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="13">
@@ -665,16 +665,16 @@
         <v>422</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>23.9821</v>
+        <v>24.1477</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>99.8266</v>
+        <v>101.2127</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0316</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -682,16 +682,16 @@
         <v>424</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>22.3949</v>
+        <v>22.5381</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>108.0789</v>
+        <v>109.5069</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0313</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.0977</v>
+        <v>0.09719999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -699,16 +699,16 @@
         <v>426</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>21.0072</v>
+        <v>21.1328</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>117.1338</v>
+        <v>118.6104</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.0311</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.1021</v>
+        <v>0.1016</v>
       </c>
     </row>
     <row r="16">
@@ -716,16 +716,16 @@
         <v>428</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>19.6886</v>
+        <v>19.8028</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>127.2389</v>
+        <v>128.7647</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0308</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.1067</v>
+        <v>0.1062</v>
       </c>
     </row>
     <row r="17">
@@ -733,16 +733,16 @@
         <v>430</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>18.5626</v>
+        <v>18.6724</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>137.8687</v>
+        <v>139.4413</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0305</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.1113</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="18">
@@ -750,16 +750,16 @@
         <v>432</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>17.5371</v>
+        <v>17.6516</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>149.7418</v>
+        <v>151.3474</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.0302</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.1155</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="19">
@@ -767,16 +767,16 @@
         <v>434</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>16.8676</v>
+        <v>16.9969</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>161.7959</v>
+        <v>163.4129</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0299</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.1186</v>
+        <v>0.1178</v>
       </c>
     </row>
     <row r="20">
@@ -784,16 +784,16 @@
         <v>436</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>16.4454</v>
+        <v>16.596</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>174.8546</v>
+        <v>176.4397</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.0297</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.12</v>
+        <v>0.1191</v>
       </c>
     </row>
     <row r="21">
@@ -801,16 +801,16 @@
         <v>438</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>16.4001</v>
+        <v>16.5737</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>187.6972</v>
+        <v>189.2057</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.0294</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.1195</v>
+        <v>0.1184</v>
       </c>
     </row>
     <row r="22">
@@ -818,16 +818,16 @@
         <v>440</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>16.5834</v>
+        <v>16.7747</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>200.2198</v>
+        <v>201.6145</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0291</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.117</v>
+        <v>0.1158</v>
       </c>
     </row>
     <row r="23">
@@ -835,16 +835,16 @@
         <v>442</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>17.0251</v>
+        <v>17.2036</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>212.1945</v>
+        <v>213.5001</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0288</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.1128</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="24">
@@ -852,16 +852,16 @@
         <v>444</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>17.883</v>
+        <v>18.0441</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>223.3631</v>
+        <v>224.581</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.0286</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.1076</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="25">
@@ -869,16 +869,16 @@
         <v>446</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>18.7484</v>
+        <v>18.8905</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>233.4719</v>
+        <v>234.6061</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0283</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.1021</v>
+        <v>0.1014</v>
       </c>
     </row>
     <row r="26">
@@ -886,16 +886,16 @@
         <v>448</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>19.8727</v>
+        <v>19.9953</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>242.8461</v>
+        <v>243.9015</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0281</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0961</v>
       </c>
     </row>
     <row r="27">
@@ -903,16 +903,16 @@
         <v>450</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>21.0702</v>
+        <v>21.1741</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>251.1898</v>
+        <v>252.1746</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.0278</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -920,16 +920,16 @@
         <v>452</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>22.241</v>
+        <v>22.3279</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>258.75</v>
+        <v>259.6705</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0275</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.0864</v>
+        <v>0.0862</v>
       </c>
     </row>
     <row r="29">
@@ -937,16 +937,16 @@
         <v>454</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>23.5304</v>
+        <v>23.6028</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>265.5281</v>
+        <v>266.3896</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0273</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.082</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="30">
@@ -954,16 +954,16 @@
         <v>456</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>24.894</v>
+        <v>24.9548</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>271.7893</v>
+        <v>272.5973</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.027</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.0779</v>
+        <v>0.07779999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -971,16 +971,16 @@
         <v>458</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>26.2772</v>
+        <v>26.3294</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>277.623</v>
+        <v>278.3843</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0268</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.0742</v>
+        <v>0.0741</v>
       </c>
     </row>
     <row r="32">
@@ -988,10 +988,10 @@
         <v>460</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>27.8134</v>
+        <v>27.8595</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>282.9978</v>
+        <v>283.7236</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0266</v>
@@ -1005,10 +1005,10 @@
         <v>462</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>29.4843</v>
+        <v>29.5246</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>287.9044</v>
+        <v>288.633</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.0263</v>
@@ -1022,16 +1022,16 @@
         <v>464</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>31.2654</v>
+        <v>31.3026</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>292.61</v>
+        <v>293.3578</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0261</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.0646</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="35">
@@ -1039,10 +1039,10 @@
         <v>466</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>33.3851</v>
+        <v>33.4201</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>297.4125</v>
+        <v>298.1997</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0258</v>
@@ -1056,10 +1056,10 @@
         <v>468</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>35.7624</v>
+        <v>35.7923</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>302.2087</v>
+        <v>303.0628</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0256</v>
@@ -1073,10 +1073,10 @@
         <v>470</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>38.5249</v>
+        <v>38.5395</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>307.5838</v>
+        <v>308.5388</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0254</v>
@@ -1090,10 +1090,10 @@
         <v>472</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>41.5977</v>
+        <v>41.575</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>313.7284</v>
+        <v>314.8184</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.0251</v>
@@ -1107,10 +1107,10 @@
         <v>474</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>44.9579</v>
+        <v>44.8593</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>321.6388</v>
+        <v>322.8819</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0249</v>
@@ -1124,16 +1124,16 @@
         <v>476</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>48.1695</v>
+        <v>47.9424</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>331.4014</v>
+        <v>332.7685</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0247</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.0547</v>
+        <v>0.0546</v>
       </c>
     </row>
     <row r="41">
@@ -1141,16 +1141,16 @@
         <v>478</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>50.6783</v>
+        <v>50.2776</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>343.9225</v>
+        <v>345.291</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0245</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.0549</v>
+        <v>0.0548</v>
       </c>
     </row>
     <row r="42">
@@ -1158,16 +1158,16 @@
         <v>480</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>51.6373</v>
+        <v>51.0693</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>358.1762</v>
+        <v>359.343</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0242</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.0548</v>
+        <v>0.0546</v>
       </c>
     </row>
     <row r="43">
@@ -1175,16 +1175,16 @@
         <v>482</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>50.7618</v>
+        <v>50.1114</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>12.3384</v>
+        <v>13.1732</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.024</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.054</v>
+        <v>0.0537</v>
       </c>
     </row>
     <row r="44">
@@ -1192,16 +1192,16 @@
         <v>484</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>48.4329</v>
+        <v>47.7919</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>24.6109</v>
+        <v>25.1257</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0238</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.0528</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="45">
@@ -1209,10 +1209,10 @@
         <v>486</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45.3416</v>
+        <v>44.7696</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>34.4101</v>
+        <v>34.7074</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0236</v>
@@ -1226,16 +1226,16 @@
         <v>488</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>42.0797</v>
+        <v>41.5965</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>42.0301</v>
+        <v>42.2142</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0234</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.0517</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         <v>490</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>39.1145</v>
+        <v>38.7163</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>48.0255</v>
+        <v>48.1682</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0232</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.0521</v>
+        <v>0.0523</v>
       </c>
     </row>
     <row r="48">
@@ -1260,16 +1260,16 @@
         <v>492</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>36.4487</v>
+        <v>36.1245</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>53.0079</v>
+        <v>53.1522</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.023</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.0529</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="49">
@@ -1277,16 +1277,16 @@
         <v>494</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>34.0992</v>
+        <v>33.8372</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>57.3309</v>
+        <v>57.4996</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0228</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.054</v>
+        <v>0.0542</v>
       </c>
     </row>
     <row r="50">
@@ -1294,16 +1294,16 @@
         <v>496</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>32.0716</v>
+        <v>31.862</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>61.3577</v>
+        <v>61.5611</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0226</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.0552</v>
+        <v>0.0554</v>
       </c>
     </row>
     <row r="51">
@@ -1311,16 +1311,16 @@
         <v>498</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>30.234</v>
+        <v>30.069</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>65.21980000000001</v>
+        <v>65.4618</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0224</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.0566</v>
+        <v>0.0568</v>
       </c>
     </row>
     <row r="52">
@@ -1328,16 +1328,16 @@
         <v>500</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>28.5422</v>
+        <v>28.4139</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>69.08839999999999</v>
+        <v>69.36660000000001</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0222</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.0581</v>
+        <v>0.0583</v>
       </c>
     </row>
     <row r="53">
@@ -1345,16 +1345,16 @@
         <v>502</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>27.1232</v>
+        <v>27.0004</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>73.006</v>
+        <v>73.2838</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.022</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.0597</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="54">
@@ -1362,16 +1362,16 @@
         <v>504</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>25.7391</v>
+        <v>25.6175</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>76.9486</v>
+        <v>77.2259</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0218</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.0614</v>
+        <v>0.0616</v>
       </c>
     </row>
     <row r="55">
@@ -1379,16 +1379,16 @@
         <v>506</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>24.4333</v>
+        <v>24.3119</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>81.1384</v>
+        <v>81.41849999999999</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.0216</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.0634</v>
       </c>
     </row>
     <row r="56">
@@ -1396,16 +1396,16 @@
         <v>508</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>23.1749</v>
+        <v>23.0535</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>85.59229999999999</v>
+        <v>85.8779</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0215</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0654</v>
       </c>
     </row>
     <row r="57">
@@ -1413,16 +1413,16 @@
         <v>510</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>22.0164</v>
+        <v>21.8957</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>90.0801</v>
+        <v>90.3725</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0213</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.0673</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -1430,16 +1430,16 @@
         <v>512</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>20.9113</v>
+        <v>20.7922</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>94.8779</v>
+        <v>95.17870000000001</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0211</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.0696</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="59">
@@ -1447,16 +1447,16 @@
         <v>514</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>19.8079</v>
+        <v>19.6914</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>99.8421</v>
+        <v>100.1521</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0209</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.0722</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="60">
@@ -1464,16 +1464,16 @@
         <v>516</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>18.7273</v>
+        <v>18.6149</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>105.3822</v>
+        <v>105.7053</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0207</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>0.075</v>
+        <v>0.07539999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1481,16 +1481,16 @@
         <v>518</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>17.6987</v>
+        <v>17.5918</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>111.0145</v>
+        <v>111.3533</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.0206</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>0.0781</v>
+        <v>0.0785</v>
       </c>
     </row>
     <row r="62">
@@ -1498,16 +1498,16 @@
         <v>520</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>16.7206</v>
+        <v>16.6205</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>117.3032</v>
+        <v>117.6635</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0204</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>0.0814</v>
+        <v>0.0819</v>
       </c>
     </row>
     <row r="63">
@@ -1515,16 +1515,16 @@
         <v>522</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>15.8168</v>
+        <v>15.7164</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>123.9869</v>
+        <v>124.3646</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0202</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>0.0849</v>
+        <v>0.0854</v>
       </c>
     </row>
     <row r="64">
@@ -1532,16 +1532,16 @@
         <v>524</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>15.0048</v>
+        <v>14.9053</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>130.9724</v>
+        <v>131.3722</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0201</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0.0885</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="65">
@@ -1549,16 +1549,16 @@
         <v>526</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>14.2173</v>
+        <v>14.1209</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>138.5933</v>
+        <v>139.0212</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0199</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>0.092</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row r="66">
@@ -1566,16 +1566,16 @@
         <v>528</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>13.6005</v>
+        <v>13.5091</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>146.8891</v>
+        <v>147.3492</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0198</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>0.0953</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="67">
@@ -1583,16 +1583,16 @@
         <v>530</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>13.0658</v>
+        <v>12.9807</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>155.2281</v>
+        <v>155.7169</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0196</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>0.098</v>
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -1600,16 +1600,16 @@
         <v>532</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>12.7064</v>
+        <v>12.6291</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>164.3807</v>
+        <v>164.897</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.0195</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>0.1001</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="69">
@@ -1617,16 +1617,16 @@
         <v>534</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>12.4202</v>
+        <v>12.3518</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>173.6131</v>
+        <v>174.1487</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0193</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0.1011</v>
+        <v>0.1016</v>
       </c>
     </row>
     <row r="70">
@@ -1634,16 +1634,16 @@
         <v>536</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>12.3216</v>
+        <v>12.2632</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>183.0657</v>
+        <v>183.6107</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0192</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0.1009</v>
+        <v>0.1014</v>
       </c>
     </row>
     <row r="71">
@@ -1651,16 +1651,16 @@
         <v>538</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>12.4132</v>
+        <v>12.3655</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>192.2339</v>
+        <v>192.7746</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.019</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="72">
@@ -1668,16 +1668,16 @@
         <v>540</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>12.6566</v>
+        <v>12.6195</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>201.1243</v>
+        <v>201.6486</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0189</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0975</v>
       </c>
     </row>
     <row r="73">
@@ -1685,16 +1685,16 @@
         <v>542</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>12.9765</v>
+        <v>12.9422</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>209.8426</v>
+        <v>210.3576</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.0187</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>0.094</v>
+        <v>0.09420000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -1702,16 +1702,16 @@
         <v>544</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>13.4987</v>
+        <v>13.4668</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>217.9051</v>
+        <v>218.4056</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0186</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>0.0902</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -1719,16 +1719,16 @@
         <v>546</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>14.0608</v>
+        <v>14.0314</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>225.2837</v>
+        <v>225.7644</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0185</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>0.0862</v>
+        <v>0.0863</v>
       </c>
     </row>
     <row r="76">
@@ -1736,16 +1736,16 @@
         <v>548</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>14.6535</v>
+        <v>14.6263</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>232.171</v>
+        <v>232.6291</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0183</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0822</v>
       </c>
     </row>
     <row r="77">
@@ -1753,16 +1753,16 @@
         <v>550</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>15.4654</v>
+        <v>15.4403</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>238.5776</v>
+        <v>239.0116</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.0182</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.0781</v>
+        <v>0.07820000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -1770,16 +1770,16 @@
         <v>552</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>16.1808</v>
+        <v>16.1577</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>244.46</v>
+        <v>244.8694</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.0181</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>0.0742</v>
+        <v>0.0743</v>
       </c>
     </row>
     <row r="79">
@@ -1787,10 +1787,10 @@
         <v>554</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>16.9498</v>
+        <v>16.9287</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>250.0634</v>
+        <v>250.448</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0179</v>
@@ -1804,16 +1804,16 @@
         <v>556</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>17.822</v>
+        <v>17.803</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>255.2287</v>
+        <v>255.5886</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0178</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.0673</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="81">
@@ -1821,10 +1821,10 @@
         <v>558</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>18.6674</v>
+        <v>18.6506</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>259.9265</v>
+        <v>260.2622</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0177</v>
@@ -1838,10 +1838,10 @@
         <v>560</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>19.5134</v>
+        <v>19.4982</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>264.3926</v>
+        <v>264.7052</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0176</v>
@@ -1855,10 +1855,10 @@
         <v>562</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>20.3925</v>
+        <v>20.3766</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>268.6179</v>
+        <v>268.9127</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0175</v>
@@ -1872,10 +1872,10 @@
         <v>564</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>21.2752</v>
+        <v>21.2583</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>272.344</v>
+        <v>272.6221</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0174</v>
@@ -1889,10 +1889,10 @@
         <v>566</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>22.1846</v>
+        <v>22.167</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>276.0786</v>
+        <v>276.3409</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0173</v>
@@ -1906,10 +1906,10 @@
         <v>568</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>23.088</v>
+        <v>23.0702</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>279.5247</v>
+        <v>279.7718</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0172</v>
@@ -1923,10 +1923,10 @@
         <v>570</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>24.0358</v>
+        <v>24.0182</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>282.913</v>
+        <v>283.1457</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.017</v>
@@ -1940,10 +1940,10 @@
         <v>572</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>24.9802</v>
+        <v>24.9637</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>286.1614</v>
+        <v>286.3802</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0169</v>
@@ -1957,10 +1957,10 @@
         <v>574</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>25.9952</v>
+        <v>25.9802</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>289.1559</v>
+        <v>289.361</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.0168</v>
@@ -1974,10 +1974,10 @@
         <v>576</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>26.9768</v>
+        <v>26.9639</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>292.1559</v>
+        <v>292.3477</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0168</v>
@@ -1991,10 +1991,10 @@
         <v>578</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>28.0853</v>
+        <v>28.0746</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>295.1085</v>
+        <v>295.2875</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0167</v>
@@ -2008,10 +2008,10 @@
         <v>580</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>29.1847</v>
+        <v>29.1763</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>298.0341</v>
+        <v>298.2012</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0166</v>
@@ -2025,10 +2025,10 @@
         <v>582</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>30.4053</v>
+        <v>30.3982</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>300.9917</v>
+        <v>301.1528</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0165</v>
@@ -2042,16 +2042,16 @@
         <v>584</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>31.7042</v>
+        <v>31.6985</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>303.9508</v>
+        <v>304.1065</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0164</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>0.0403</v>
+        <v>0.0404</v>
       </c>
     </row>
     <row r="95">
@@ -2059,10 +2059,10 @@
         <v>586</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>33.0176</v>
+        <v>33.0135</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>306.9829</v>
+        <v>307.133</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0163</v>
@@ -2076,10 +2076,10 @@
         <v>588</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>34.4023</v>
+        <v>34.4001</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>310.3235</v>
+        <v>310.4675</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.0162</v>
@@ -2096,7 +2096,7 @@
         <v>35.9275</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>313.8029</v>
+        <v>313.9397</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0162</v>
@@ -2110,10 +2110,10 @@
         <v>592</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>37.47</v>
+        <v>37.473</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>317.6458</v>
+        <v>317.774</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0161</v>
@@ -2127,10 +2127,10 @@
         <v>594</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>39.0464</v>
+        <v>39.0535</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>321.8438</v>
+        <v>321.9615</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.016</v>
@@ -2144,10 +2144,10 @@
         <v>596</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>40.5817</v>
+        <v>40.5945</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>326.4655</v>
+        <v>326.5717</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0159</v>
@@ -2161,10 +2161,10 @@
         <v>598</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>42.0535</v>
+        <v>42.0741</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>331.6365</v>
+        <v>331.7316</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0159</v>
@@ -2178,10 +2178,10 @@
         <v>600</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>43.3694</v>
+        <v>43.3975</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>337.3888</v>
+        <v>337.4772</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0158</v>
@@ -2195,10 +2195,10 @@
         <v>602</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>44.461</v>
+        <v>44.4662</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>343.5718</v>
+        <v>343.679</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0157</v>
@@ -2212,10 +2212,10 @@
         <v>604</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45.2689</v>
+        <v>45.2449</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>350.2322</v>
+        <v>350.3513</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.0157</v>
@@ -2229,10 +2229,10 @@
         <v>606</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45.6222</v>
+        <v>45.5676</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>357.0607</v>
+        <v>357.1783</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0156</v>
@@ -2246,10 +2246,10 @@
         <v>608</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45.5586</v>
+        <v>45.4755</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>3.9523</v>
+        <v>4.0536</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0156</v>
@@ -2263,10 +2263,10 @@
         <v>610</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45.0727</v>
+        <v>44.966</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>10.7801</v>
+        <v>10.8526</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0155</v>
@@ -2280,10 +2280,10 @@
         <v>612</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>44.2041</v>
+        <v>44.0805</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>17.0014</v>
+        <v>17.0374</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0155</v>
@@ -2297,10 +2297,10 @@
         <v>614</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>43.1215</v>
+        <v>42.9879</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>22.894</v>
+        <v>22.8916</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0154</v>
@@ -2314,10 +2314,10 @@
         <v>616</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>41.7692</v>
+        <v>41.6313</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>28.1247</v>
+        <v>28.086</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0154</v>
@@ -2331,10 +2331,10 @@
         <v>618</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>40.3682</v>
+        <v>40.23</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>32.7923</v>
+        <v>32.7215</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.0153</v>
@@ -2348,10 +2348,10 @@
         <v>620</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>38.947</v>
+        <v>38.8115</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>37.0311</v>
+        <v>36.9342</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.0153</v>
@@ -2365,16 +2365,16 @@
         <v>622</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>37.4542</v>
+        <v>37.3302</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>40.7687</v>
+        <v>40.6643</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.0153</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0.0347</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="114">
@@ -2382,10 +2382,10 @@
         <v>624</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>36.0621</v>
+        <v>35.9493</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>44.2082</v>
+        <v>44.1014</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.0152</v>
@@ -2399,10 +2399,10 @@
         <v>626</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>34.7125</v>
+        <v>34.6097</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>47.2951</v>
+        <v>47.1884</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.0152</v>
@@ -2416,10 +2416,10 @@
         <v>628</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>33.4159</v>
+        <v>33.322</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>50.111</v>
+        <v>50.0062</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.0152</v>
@@ -2433,16 +2433,16 @@
         <v>630</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>32.2047</v>
+        <v>32.1185</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>52.7367</v>
+        <v>52.6351</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>0.0369</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="118">
@@ -2450,10 +2450,10 @@
         <v>632</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>31.0344</v>
+        <v>30.9549</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>55.2679</v>
+        <v>55.1703</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.0151</v>
@@ -2467,16 +2467,16 @@
         <v>634</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>29.9882</v>
+        <v>29.9146</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>57.7429</v>
+        <v>57.6499</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="120">
@@ -2484,16 +2484,16 @@
         <v>636</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>28.9785</v>
+        <v>28.9102</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>60.0619</v>
+        <v>59.9736</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.0151</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.0391</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="121">
@@ -2501,16 +2501,16 @@
         <v>638</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>28.0132</v>
+        <v>27.9497</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>62.3337</v>
+        <v>62.2501</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="122">
@@ -2518,10 +2518,10 @@
         <v>640</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>27.097</v>
+        <v>27.0376</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>64.55240000000001</v>
+        <v>64.4729</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.015</v>
@@ -2535,10 +2535,10 @@
         <v>642</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>26.2011</v>
+        <v>26.1405</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>66.84520000000001</v>
+        <v>66.7615</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.015</v>
@@ -2552,16 +2552,16 @@
         <v>644</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>25.3908</v>
+        <v>25.3285</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>69.1147</v>
+        <v>69.026</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>0.0426</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="125">
@@ -2569,16 +2569,16 @@
         <v>646</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>24.5826</v>
+        <v>24.5187</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>71.3663</v>
+        <v>71.2727</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>0.0436</v>
+        <v>0.0437</v>
       </c>
     </row>
     <row r="126">
@@ -2586,16 +2586,16 @@
         <v>648</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>23.8161</v>
+        <v>23.7506</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>73.6687</v>
+        <v>73.5702</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>0.0447</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="127">
@@ -2603,16 +2603,16 @@
         <v>650</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>23.0563</v>
+        <v>22.9893</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>76.0458</v>
+        <v>75.9426</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>0.0458</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="128">
@@ -2620,16 +2620,16 @@
         <v>652</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>22.3154</v>
+        <v>22.2468</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>78.4559</v>
+        <v>78.34780000000001</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>0.047</v>
+        <v>0.0471</v>
       </c>
     </row>
     <row r="129">
@@ -2637,16 +2637,16 @@
         <v>654</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>21.5744</v>
+        <v>21.5044</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>80.7902</v>
+        <v>80.67700000000001</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>0.0482</v>
+        <v>0.0483</v>
       </c>
     </row>
     <row r="130">
@@ -2654,16 +2654,16 @@
         <v>656</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>20.8719</v>
+        <v>20.8006</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>83.22880000000001</v>
+        <v>83.11060000000001</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.0495</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="131">
@@ -2671,16 +2671,16 @@
         <v>658</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>20.2123</v>
+        <v>20.1399</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>85.688</v>
+        <v>85.5647</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>0.0509</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="132">
@@ -2688,16 +2688,16 @@
         <v>660</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>19.5257</v>
+        <v>19.4523</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>88.4186</v>
+        <v>88.2908</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>0.0524</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="133">
@@ -2705,16 +2705,16 @@
         <v>662</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>18.8434</v>
+        <v>18.7692</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>91.1313</v>
+        <v>90.999</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>0.054</v>
+        <v>0.0542</v>
       </c>
     </row>
     <row r="134">
@@ -2722,16 +2722,16 @@
         <v>664</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>18.1835</v>
+        <v>18.1088</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>93.9478</v>
+        <v>93.81140000000001</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>0.0556</v>
+        <v>0.0558</v>
       </c>
     </row>
     <row r="135">
@@ -2739,16 +2739,16 @@
         <v>666</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>17.5628</v>
+        <v>17.4877</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>96.77119999999999</v>
+        <v>96.6306</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0.0574</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="136">
@@ -2756,16 +2756,16 @@
         <v>668</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>16.9243</v>
+        <v>16.8489</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>99.6918</v>
+        <v>99.547</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>0.0593</v>
+        <v>0.0595</v>
       </c>
     </row>
     <row r="137">
@@ -2773,16 +2773,16 @@
         <v>670</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>16.2573</v>
+        <v>16.1813</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>102.7964</v>
+        <v>102.6478</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>0.0613</v>
+        <v>0.0616</v>
       </c>
     </row>
     <row r="138">
@@ -2790,16 +2790,16 @@
         <v>672</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>15.6775</v>
+        <v>15.6006</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>106.0358</v>
+        <v>105.8834</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>0.0634</v>
+        <v>0.06370000000000001</v>
       </c>
     </row>
     <row r="139">
@@ -2807,16 +2807,16 @@
         <v>674</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>15.06</v>
+        <v>14.982</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>109.453</v>
+        <v>109.2974</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="140">
@@ -2824,16 +2824,16 @@
         <v>676</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>14.5054</v>
+        <v>14.4263</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>113.0728</v>
+        <v>112.9151</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="141">
@@ -2841,16 +2841,16 @@
         <v>678</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>13.9443</v>
+        <v>13.8642</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>116.8478</v>
+        <v>116.6892</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>0.0706</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -2858,16 +2858,16 @@
         <v>680</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>13.3752</v>
+        <v>13.2946</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>120.6212</v>
+        <v>120.4631</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>0.0733</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="143">
@@ -2875,16 +2875,16 @@
         <v>682</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>12.8823</v>
+        <v>12.8042</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>124.6551</v>
+        <v>124.5066</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>0.076</v>
+        <v>0.0764</v>
       </c>
     </row>
     <row r="144">
@@ -2892,16 +2892,16 @@
         <v>684</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>12.3691</v>
+        <v>12.2941</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>128.9965</v>
+        <v>128.8605</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>0.0789</v>
+        <v>0.0793</v>
       </c>
     </row>
     <row r="145">
@@ -2909,16 +2909,16 @@
         <v>686</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>11.9034</v>
+        <v>11.832</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>133.3879</v>
+        <v>133.2657</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0822</v>
       </c>
     </row>
     <row r="146">
@@ -2926,16 +2926,16 @@
         <v>688</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>11.4896</v>
+        <v>11.4223</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>138.1522</v>
+        <v>138.0472</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0851</v>
       </c>
     </row>
     <row r="147">
@@ -2943,16 +2943,16 @@
         <v>690</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>11.0815</v>
+        <v>11.0193</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>143.1205</v>
+        <v>143.0351</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -2960,16 +2960,16 @@
         <v>692</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>10.7169</v>
+        <v>10.6611</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>148.4769</v>
+        <v>148.4141</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.0902</v>
+        <v>0.0907</v>
       </c>
     </row>
     <row r="149">
@@ -2977,16 +2977,16 @@
         <v>694</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>10.4231</v>
+        <v>10.3748</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>153.5423</v>
+        <v>153.5006</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>0.0927</v>
+        <v>0.0931</v>
       </c>
     </row>
     <row r="150">
@@ -2994,16 +2994,16 @@
         <v>696</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>10.1595</v>
+        <v>10.1197</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>159.4149</v>
+        <v>159.3953</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>0.0949</v>
+        <v>0.0953</v>
       </c>
     </row>
     <row r="151">
@@ -3011,16 +3011,16 @@
         <v>698</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>9.9636</v>
+        <v>9.9323</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>165.08</v>
+        <v>165.0769</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>0.0968</v>
+        <v>0.09710000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -3028,16 +3028,16 @@
         <v>700</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>9.843999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>170.8766</v>
+        <v>170.8846</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="153">
@@ -3045,16 +3045,16 @@
         <v>702</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>9.7494</v>
+        <v>9.722</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>176.853</v>
+        <v>176.8685</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0.0989</v>
+        <v>0.09909999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -3062,16 +3062,16 @@
         <v>704</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>9.746499999999999</v>
+        <v>9.7143</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>182.8241</v>
+        <v>182.8497</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>0.099</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="155">
@@ -3079,16 +3079,16 @@
         <v>706</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>9.794600000000001</v>
+        <v>9.7576</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>188.7465</v>
+        <v>188.785</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.099</v>
       </c>
     </row>
     <row r="156">
@@ -3096,16 +3096,16 @@
         <v>708</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>9.8757</v>
+        <v>9.8344</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>194.4628</v>
+        <v>194.516</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>0.0977</v>
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -3113,16 +3113,16 @@
         <v>710</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>10.0379</v>
+        <v>9.993499999999999</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>200.0399</v>
+        <v>200.1084</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>0.0963</v>
+        <v>0.09669999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -3130,16 +3130,16 @@
         <v>712</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>10.2306</v>
+        <v>10.1844</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>205.6211</v>
+        <v>205.7044</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>0.0945</v>
+        <v>0.0949</v>
       </c>
     </row>
     <row r="159">
@@ -3147,16 +3147,16 @@
         <v>714</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>10.4723</v>
+        <v>10.4252</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>210.8159</v>
+        <v>210.911</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.0924</v>
+        <v>0.09279999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -3164,16 +3164,16 @@
         <v>716</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>10.7566</v>
+        <v>10.7092</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>215.6287</v>
+        <v>215.7328</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>0.09</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="161">
@@ -3181,16 +3181,16 @@
         <v>718</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>11.0408</v>
+        <v>10.9933</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>220.5084</v>
+        <v>220.6214</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>0.0876</v>
+        <v>0.08790000000000001</v>
       </c>
     </row>
     <row r="162">
@@ -3198,16 +3198,16 @@
         <v>720</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>11.4429</v>
+        <v>11.3952</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>225.1371</v>
+        <v>225.2584</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0854</v>
       </c>
     </row>
     <row r="163">
@@ -3215,16 +3215,16 @@
         <v>722</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>11.8255</v>
+        <v>11.7771</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>229.3121</v>
+        <v>229.4396</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>0.0825</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="164">
@@ -3232,16 +3232,16 @@
         <v>724</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>12.1857</v>
+        <v>12.1366</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>233.233</v>
+        <v>233.3663</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>0.0799</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="165">
@@ -3249,16 +3249,16 @@
         <v>726</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>12.6105</v>
+        <v>12.5608</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>237.1752</v>
+        <v>237.3141</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>0.0774</v>
+        <v>0.07770000000000001</v>
       </c>
     </row>
     <row r="166">
@@ -3266,16 +3266,16 @@
         <v>728</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>13.0285</v>
+        <v>12.9784</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>240.8021</v>
+        <v>240.9447</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>0.075</v>
+        <v>0.07530000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -3283,16 +3283,16 @@
         <v>730</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>13.5024</v>
+        <v>13.4521</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>244.1991</v>
+        <v>244.3433</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>0.0727</v>
+        <v>0.07290000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -3300,16 +3300,16 @@
         <v>732</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>13.9723</v>
+        <v>13.9222</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>247.4458</v>
+        <v>247.5896</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0707</v>
       </c>
     </row>
     <row r="169">
@@ -3317,16 +3317,16 @@
         <v>734</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>14.4253</v>
+        <v>14.3757</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>250.5426</v>
+        <v>250.6845</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.0684</v>
+        <v>0.06859999999999999</v>
       </c>
     </row>
     <row r="170">
@@ -3334,16 +3334,16 @@
         <v>736</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>14.9021</v>
+        <v>14.8532</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>253.4561</v>
+        <v>253.595</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>0.0664</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="171">
@@ -3351,16 +3351,16 @@
         <v>738</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>15.392</v>
+        <v>15.3438</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>256.2904</v>
+        <v>256.4262</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>0.0645</v>
+        <v>0.06469999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -3368,16 +3368,16 @@
         <v>740</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>15.8782</v>
+        <v>15.8302</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>258.8784</v>
+        <v>259.0115</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="173">
@@ -3385,16 +3385,16 @@
         <v>742</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>16.3718</v>
+        <v>16.3214</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>261.4235</v>
+        <v>261.5617</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>0.0611</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="174">
@@ -3402,16 +3402,16 @@
         <v>744</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>16.844</v>
+        <v>16.7909</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>263.8313</v>
+        <v>263.9753</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>0.0595</v>
+        <v>0.0596</v>
       </c>
     </row>
     <row r="175">
@@ -3419,16 +3419,16 @@
         <v>746</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>17.334</v>
+        <v>17.2781</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>266.1928</v>
+        <v>266.3422</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>0.058</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="176">
@@ -3436,16 +3436,16 @@
         <v>748</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>17.8384</v>
+        <v>17.78</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>268.4553</v>
+        <v>268.6095</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>0.0566</v>
+        <v>0.0567</v>
       </c>
     </row>
     <row r="177">
@@ -3453,16 +3453,16 @@
         <v>750</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>18.3564</v>
+        <v>18.2958</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>270.5742</v>
+        <v>270.7321</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>0.0552</v>
+        <v>0.0554</v>
       </c>
     </row>
     <row r="178">
@@ -3470,16 +3470,16 @@
         <v>752</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>18.8452</v>
+        <v>18.7828</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>272.6304</v>
+        <v>272.7911</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>0.054</v>
+        <v>0.0541</v>
       </c>
     </row>
     <row r="179">
@@ -3487,16 +3487,16 @@
         <v>754</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>19.3302</v>
+        <v>19.2664</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>274.5399</v>
+        <v>274.7024</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>0.0528</v>
+        <v>0.0529</v>
       </c>
     </row>
     <row r="180">
@@ -3504,16 +3504,16 @@
         <v>756</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>19.841</v>
+        <v>19.7759</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>276.6669</v>
+        <v>276.8316</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>0.0517</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="181">
@@ -3521,16 +3521,16 @@
         <v>758</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>20.3499</v>
+        <v>20.2834</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>278.495</v>
+        <v>278.6612</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>0.0506</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="182">
@@ -3538,16 +3538,16 @@
         <v>760</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>20.8442</v>
+        <v>20.7763</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>280.2846</v>
+        <v>280.4525</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>0.0496</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="183">
@@ -3555,16 +3555,16 @@
         <v>762</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>21.3675</v>
+        <v>21.2979</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>282.0765</v>
+        <v>282.2469</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>0.0486</v>
+        <v>0.0488</v>
       </c>
     </row>
     <row r="184">
@@ -3572,16 +3572,16 @@
         <v>764</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>21.8824</v>
+        <v>21.8108</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>283.8253</v>
+        <v>283.9984</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>0.0477</v>
+        <v>0.0479</v>
       </c>
     </row>
     <row r="185">
@@ -3589,16 +3589,16 @@
         <v>766</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>22.3966</v>
+        <v>22.3231</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>285.4588</v>
+        <v>285.6343</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>0.0469</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="186">
@@ -3606,16 +3606,16 @@
         <v>768</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>22.9011</v>
+        <v>22.8256</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>287.1827</v>
+        <v>287.3608</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>0.046</v>
+        <v>0.0461</v>
       </c>
     </row>
     <row r="187">
@@ -3623,16 +3623,16 @@
         <v>770</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>23.438</v>
+        <v>23.3608</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>288.7901</v>
+        <v>288.97</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>0.0452</v>
+        <v>0.0453</v>
       </c>
     </row>
     <row r="188">
@@ -3640,16 +3640,16 @@
         <v>772</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>23.9455</v>
+        <v>23.8668</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>290.3801</v>
+        <v>290.561</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>0.0445</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="189">
@@ -3657,16 +3657,16 @@
         <v>774</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>24.4821</v>
+        <v>24.402</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>291.9098</v>
+        <v>292.0912</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>0.0437</v>
+        <v>0.0439</v>
       </c>
     </row>
     <row r="190">
@@ -3674,16 +3674,16 @@
         <v>776</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>25.0397</v>
+        <v>24.9584</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>293.4405</v>
+        <v>293.6222</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>0.043</v>
+        <v>0.0431</v>
       </c>
     </row>
     <row r="191">
@@ -3691,16 +3691,16 @@
         <v>778</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>25.6035</v>
+        <v>25.5208</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>294.9447</v>
+        <v>295.1269</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>0.0424</v>
+        <v>0.0425</v>
       </c>
     </row>
     <row r="192">
@@ -3708,16 +3708,16 @@
         <v>780</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>26.1359</v>
+        <v>26.0516</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>296.5368</v>
+        <v>296.7208</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.0417</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="193">
@@ -3725,16 +3725,16 @@
         <v>782</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>26.7119</v>
+        <v>26.6246</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>298.0059</v>
+        <v>298.1943</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>0.0411</v>
+        <v>0.0412</v>
       </c>
     </row>
     <row r="194">
@@ -3742,16 +3742,16 @@
         <v>784</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>27.2737</v>
+        <v>27.1832</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>299.5221</v>
+        <v>299.7158</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>0.0405</v>
+        <v>0.0406</v>
       </c>
     </row>
     <row r="195">
@@ -3759,16 +3759,16 @@
         <v>786</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>27.8953</v>
+        <v>27.8013</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>300.9929</v>
+        <v>301.1922</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>0.0399</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="196">
@@ -3776,16 +3776,16 @@
         <v>788</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>28.4673</v>
+        <v>28.3694</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>302.5782</v>
+        <v>302.7836</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.0394</v>
+        <v>0.0395</v>
       </c>
     </row>
     <row r="197">
@@ -3793,16 +3793,16 @@
         <v>790</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>29.0848</v>
+        <v>28.9825</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>304.0542</v>
+        <v>304.2655</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>0.0388</v>
+        <v>0.0389</v>
       </c>
     </row>
     <row r="198">
@@ -3810,16 +3810,16 @@
         <v>792</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>29.7188</v>
+        <v>29.6116</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>305.5744</v>
+        <v>305.7921</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>0.0383</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="199">
@@ -3827,16 +3827,16 @@
         <v>794</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>30.3627</v>
+        <v>30.2499</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>307.1884</v>
+        <v>307.4128</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>0.0378</v>
+        <v>0.0379</v>
       </c>
     </row>
     <row r="200">
@@ -3844,16 +3844,16 @@
         <v>796</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>30.9793</v>
+        <v>30.8603</v>
       </c>
       <c r="C200" s="2" t="n">
-        <v>308.726</v>
+        <v>308.957</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>0.0374</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="201">
@@ -3861,16 +3861,16 @@
         <v>798</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>31.6658</v>
+        <v>31.5402</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>310.3033</v>
+        <v>310.5405</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>0.0369</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="202">
@@ -3878,16 +3878,16 @@
         <v>800</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>32.3341</v>
+        <v>32.2016</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>312.0904</v>
+        <v>312.3334</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>0.0365</v>
+        <v>0.0366</v>
       </c>
     </row>
   </sheetData>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Кремний c-Si (табличные n, k); задней стороны нет (полубесконечная)</t>
+          <t>Кремний c-Si (Green 2008, 250–1450 нм); задней стороны нет (полубесконечная)</t>
         </is>
       </c>
     </row>
